--- a/xls/circular_clamped_mid.xlsx
+++ b/xls/circular_clamped_mid.xlsx
@@ -13,7 +13,7 @@
     <workbookView xWindow="380" yWindow="460" windowWidth="28040" windowHeight="17040" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
-    <sheet name="circular" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,38 +22,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="9">
-  <si>
-    <t>type w</t>
-  </si>
-  <si>
-    <t>nʷ</t>
-  </si>
-  <si>
-    <t>type φ</t>
-  </si>
-  <si>
-    <t>nᵠ</t>
-  </si>
-  <si>
-    <t>type Q</t>
-  </si>
-  <si>
-    <t>nᵛ</t>
-  </si>
-  <si>
-    <t>L₂w</t>
-  </si>
-  <si>
-    <t>L₂φ</t>
-  </si>
-  <si>
-    <t>L₂Q</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -403,39 +371,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/xls/circular_clamped_mid.xlsx
+++ b/xls/circular_clamped_mid.xlsx
@@ -13,7 +13,7 @@
     <workbookView xWindow="380" yWindow="460" windowWidth="28040" windowHeight="17040" xr2:uid="{52D9C27D-0EF6-DD41-9728-0267E68F7539}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="circular" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,6 +22,47 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12">
+  <si>
+    <t>type w</t>
+  </si>
+  <si>
+    <t>nʷ</t>
+  </si>
+  <si>
+    <t>type φ</t>
+  </si>
+  <si>
+    <t>nᵠ</t>
+  </si>
+  <si>
+    <t>type Q</t>
+  </si>
+  <si>
+    <t>nᵛ</t>
+  </si>
+  <si>
+    <t>L₂w</t>
+  </si>
+  <si>
+    <t>L₂φ</t>
+  </si>
+  <si>
+    <t>L₂Q</t>
+  </si>
+  <si>
+    <t>ReproducingKernel{:Linear2D, :□, :CubicSpline}</t>
+  </si>
+  <si>
+    <t>tri3</t>
+  </si>
+  <si>
+    <t>PiecewisePolynomial{:Quadratic2D}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -371,9 +412,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>721</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3">
+        <v>8100</v>
+      </c>
+      <c r="G3">
+        <v>-3.2447984755035377e-6</v>
+      </c>
+      <c r="H3">
+        <v>-1.3227036706264366e-6</v>
+      </c>
+      <c r="I3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6">
+        <v>721</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6">
+        <v>8100</v>
+      </c>
+      <c r="G6">
+        <v>-4.6016528068626866e-6</v>
+      </c>
+      <c r="H6">
+        <v>-2.4020020025009474e-8</v>
+      </c>
+      <c r="I6">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>271</v>
+      </c>
+      <c r="C9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>721</v>
+      </c>
+      <c r="E9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9">
+        <v>8100</v>
+      </c>
+      <c r="G9">
+        <v>-4.804660353516635e-6</v>
+      </c>
+      <c r="H9">
+        <v>6.683451392695205e-7</v>
+      </c>
+      <c r="I9">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>469</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12">
+        <v>721</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>8100</v>
+      </c>
+      <c r="G12">
+        <v>-4.890922387717054e-6</v>
+      </c>
+      <c r="H12">
+        <v>1.2556334369860315e-6</v>
+      </c>
+      <c r="I12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>721</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>721</v>
+      </c>
+      <c r="E15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15">
+        <v>8100</v>
+      </c>
+      <c r="G15">
+        <v>-4.9460918568919215e-6</v>
+      </c>
+      <c r="H15">
+        <v>1.8534060772432916e-6</v>
+      </c>
+      <c r="I15">
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/xls/circular_clamped_mid.xlsx
+++ b/xls/circular_clamped_mid.xlsx
@@ -464,10 +464,10 @@
         <v>8100</v>
       </c>
       <c r="G3">
-        <v>-3.2447984755035377e-6</v>
+        <v>-4.834885116974637e-6</v>
       </c>
       <c r="H3">
-        <v>-1.3227036706264366e-6</v>
+        <v>-1.642822506375091e-6</v>
       </c>
       <c r="I3">
         <v>0.0</v>
@@ -493,10 +493,10 @@
         <v>8100</v>
       </c>
       <c r="G6">
-        <v>-4.6016528068626866e-6</v>
+        <v>-5.100744534847537e-6</v>
       </c>
       <c r="H6">
-        <v>-2.4020020025009474e-8</v>
+        <v>1.0627125907594464e-7</v>
       </c>
       <c r="I6">
         <v>0.0</v>
@@ -522,10 +522,10 @@
         <v>8100</v>
       </c>
       <c r="G9">
-        <v>-4.804660353516635e-6</v>
+        <v>-5.143897160416161e-6</v>
       </c>
       <c r="H9">
-        <v>6.683451392695205e-7</v>
+        <v>8.58696575395898e-7</v>
       </c>
       <c r="I9">
         <v>0.0</v>
@@ -551,10 +551,10 @@
         <v>8100</v>
       </c>
       <c r="G12">
-        <v>-4.890922387717054e-6</v>
+        <v>-5.160471489662691e-6</v>
       </c>
       <c r="H12">
-        <v>1.2556334369860315e-6</v>
+        <v>1.4055527098384436e-6</v>
       </c>
       <c r="I12">
         <v>0.0</v>
@@ -580,10 +580,10 @@
         <v>8100</v>
       </c>
       <c r="G15">
-        <v>-4.9460918568919215e-6</v>
+        <v>-5.173478887357273e-6</v>
       </c>
       <c r="H15">
-        <v>1.8534060772432916e-6</v>
+        <v>2.0089761107310793e-6</v>
       </c>
       <c r="I15">
         <v>0.0</v>
